--- a/experiments/qiskit_test.xlsx
+++ b/experiments/qiskit_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lvuorenk/Documents/vaikkari/paulioptnew/pauliopt/experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9B778B0C-22E0-6D48-868A-405D0642F8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{2AE374EB-F6FC-1144-8940-C51E486CC372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1180" windowWidth="27640" windowHeight="16640" activeTab="1" xr2:uid="{C03A00C5-0B13-9E41-9CA7-E1380018330A}"/>
   </bookViews>
@@ -16,7 +16,20 @@
     <sheet name="count" sheetId="2" r:id="rId1"/>
     <sheet name="depth" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -707,34 +720,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>243.4</c:v>
+                  <c:v>272.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>556.20000000000005</c:v>
+                  <c:v>610.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>848.7</c:v>
+                  <c:v>897.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1159.0999999999999</c:v>
+                  <c:v>1176.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1496.6</c:v>
+                  <c:v>1481.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1791</c:v>
+                  <c:v>1810.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2140.8000000000002</c:v>
+                  <c:v>2206.1999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2430.5</c:v>
+                  <c:v>2512.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2803.6</c:v>
+                  <c:v>2851.7</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2934</c:v>
+                  <c:v>3166.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -818,34 +831,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>356.4</c:v>
+                  <c:v>417</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>915.6</c:v>
+                  <c:v>974.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1501.4</c:v>
+                  <c:v>1500.8</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2039.6</c:v>
+                  <c:v>2100</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2591.8000000000002</c:v>
+                  <c:v>2669.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3101</c:v>
+                  <c:v>3167.4</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3684.6</c:v>
+                  <c:v>3668.3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4241.6000000000004</c:v>
+                  <c:v>4288.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>4943.1000000000004</c:v>
+                  <c:v>4900.3999999999996</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>5330.8</c:v>
+                  <c:v>5476.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -929,34 +942,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>273.8</c:v>
+                  <c:v>289.7</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>467.2</c:v>
+                  <c:v>500.2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>604.4</c:v>
+                  <c:v>617.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>735.2</c:v>
+                  <c:v>741.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>850</c:v>
+                  <c:v>866.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>974.4</c:v>
+                  <c:v>974.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1097</c:v>
+                  <c:v>1099.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1200.8</c:v>
+                  <c:v>1233</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1347.1</c:v>
+                  <c:v>1361.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1431.4</c:v>
+                  <c:v>1493</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1040,34 +1053,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>267.60000000000002</c:v>
+                  <c:v>287.39999999999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>408.4</c:v>
+                  <c:v>430.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>508.4</c:v>
+                  <c:v>516.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>604.79999999999995</c:v>
+                  <c:v>612</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>691</c:v>
+                  <c:v>700.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>778.6</c:v>
+                  <c:v>779.9</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>871.1</c:v>
+                  <c:v>871.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>946</c:v>
+                  <c:v>962.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1060.5999999999999</c:v>
+                  <c:v>1057.8</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1112.5999999999999</c:v>
+                  <c:v>1150.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1151,34 +1164,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>342</c:v>
+                  <c:v>394</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>714.7</c:v>
+                  <c:v>817.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1122.9000000000001</c:v>
+                  <c:v>1163.5999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1427.1</c:v>
+                  <c:v>1565.3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1769.6</c:v>
+                  <c:v>1889.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2135.4</c:v>
+                  <c:v>2206.8000000000002</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2426.1999999999998</c:v>
+                  <c:v>2564.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2724.4</c:v>
+                  <c:v>2813.3</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3140</c:v>
+                  <c:v>3113.1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3248.6</c:v>
+                  <c:v>3455</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1514,34 +1527,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>169.6</c:v>
+                  <c:v>208.4</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>366.4</c:v>
+                  <c:v>449.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>566.6</c:v>
+                  <c:v>665</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>772.4</c:v>
+                  <c:v>867.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>986.2</c:v>
+                  <c:v>1077.0999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1172.3</c:v>
+                  <c:v>1294.7</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1410.4</c:v>
+                  <c:v>1592.4</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1581</c:v>
+                  <c:v>1813</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1863.4</c:v>
+                  <c:v>2094.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1920.4</c:v>
+                  <c:v>2293.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1625,34 +1638,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>197.6</c:v>
+                  <c:v>224.8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>478</c:v>
+                  <c:v>504.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>789.9</c:v>
+                  <c:v>785.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1049.9000000000001</c:v>
+                  <c:v>1074.4000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1330.9</c:v>
+                  <c:v>1377.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1586.2</c:v>
+                  <c:v>1639.1</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1859.4</c:v>
+                  <c:v>1885.2</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2139.4</c:v>
+                  <c:v>2185.9</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2515.1999999999998</c:v>
+                  <c:v>2489.9</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2719.1</c:v>
+                  <c:v>2803.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1736,34 +1749,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>128.80000000000001</c:v>
+                  <c:v>130.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>186.6</c:v>
+                  <c:v>200.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>232.6</c:v>
+                  <c:v>231.4</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>268.2</c:v>
+                  <c:v>273.39999999999998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>299</c:v>
+                  <c:v>308.60000000000002</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>351.4</c:v>
+                  <c:v>347</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>385.1</c:v>
+                  <c:v>375.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>421.2</c:v>
+                  <c:v>423.6</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>468.2</c:v>
+                  <c:v>459.1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>504.9</c:v>
+                  <c:v>497.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1847,34 +1860,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>140</c:v>
+                  <c:v>147.30000000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197.2</c:v>
+                  <c:v>205.4</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>247.4</c:v>
+                  <c:v>250.7</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>292.39999999999998</c:v>
+                  <c:v>296</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>339.2</c:v>
+                  <c:v>341.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>381.4</c:v>
+                  <c:v>379</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>428.1</c:v>
+                  <c:v>418.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>467.6</c:v>
+                  <c:v>470.7</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>524</c:v>
+                  <c:v>517.4</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>559.20000000000005</c:v>
+                  <c:v>569</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1958,34 +1971,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>148.5</c:v>
+                  <c:v>181.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>315.8</c:v>
+                  <c:v>356.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>477.9</c:v>
+                  <c:v>501</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>608.6</c:v>
+                  <c:v>673.4</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>743.5</c:v>
+                  <c:v>815.2</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>913.2</c:v>
+                  <c:v>953.8</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1049.2</c:v>
+                  <c:v>1101.3</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1170.5999999999999</c:v>
+                  <c:v>1208.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>1346.1</c:v>
+                  <c:v>1352.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1394</c:v>
+                  <c:v>1473.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3738,19 +3751,19 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>243.4</v>
+        <v>272.8</v>
       </c>
       <c r="C2">
-        <v>356.4</v>
+        <v>417</v>
       </c>
       <c r="D2">
-        <v>273.8</v>
+        <v>289.7</v>
       </c>
       <c r="E2">
-        <v>267.60000000000002</v>
+        <v>287.39999999999998</v>
       </c>
       <c r="F2">
-        <v>342</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3758,19 +3771,19 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>556.20000000000005</v>
+        <v>610.4</v>
       </c>
       <c r="C3">
-        <v>915.6</v>
+        <v>974.8</v>
       </c>
       <c r="D3">
-        <v>467.2</v>
+        <v>500.2</v>
       </c>
       <c r="E3">
-        <v>408.4</v>
+        <v>430.8</v>
       </c>
       <c r="F3">
-        <v>714.7</v>
+        <v>817.9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -3778,19 +3791,19 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>848.7</v>
+        <v>897.9</v>
       </c>
       <c r="C4">
-        <v>1501.4</v>
+        <v>1500.8</v>
       </c>
       <c r="D4">
-        <v>604.4</v>
+        <v>617.6</v>
       </c>
       <c r="E4">
-        <v>508.4</v>
+        <v>516.6</v>
       </c>
       <c r="F4">
-        <v>1122.9000000000001</v>
+        <v>1163.5999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -3798,19 +3811,19 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>1159.0999999999999</v>
+        <v>1176.8</v>
       </c>
       <c r="C5">
-        <v>2039.6</v>
+        <v>2100</v>
       </c>
       <c r="D5">
-        <v>735.2</v>
+        <v>741.9</v>
       </c>
       <c r="E5">
-        <v>604.79999999999995</v>
+        <v>612</v>
       </c>
       <c r="F5">
-        <v>1427.1</v>
+        <v>1565.3</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -3818,19 +3831,19 @@
         <v>50</v>
       </c>
       <c r="B6">
-        <v>1496.6</v>
+        <v>1481.4</v>
       </c>
       <c r="C6">
-        <v>2591.8000000000002</v>
+        <v>2669.4</v>
       </c>
       <c r="D6">
-        <v>850</v>
+        <v>866.5</v>
       </c>
       <c r="E6">
-        <v>691</v>
+        <v>700.2</v>
       </c>
       <c r="F6">
-        <v>1769.6</v>
+        <v>1889.4</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -3838,19 +3851,19 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>1791</v>
+        <v>1810.4</v>
       </c>
       <c r="C7">
-        <v>3101</v>
+        <v>3167.4</v>
       </c>
       <c r="D7">
-        <v>974.4</v>
+        <v>974.8</v>
       </c>
       <c r="E7">
-        <v>778.6</v>
+        <v>779.9</v>
       </c>
       <c r="F7">
-        <v>2135.4</v>
+        <v>2206.8000000000002</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -3858,19 +3871,19 @@
         <v>70</v>
       </c>
       <c r="B8">
-        <v>2140.8000000000002</v>
+        <v>2206.1999999999998</v>
       </c>
       <c r="C8">
-        <v>3684.6</v>
+        <v>3668.3</v>
       </c>
       <c r="D8">
-        <v>1097</v>
+        <v>1099.5999999999999</v>
       </c>
       <c r="E8">
-        <v>871.1</v>
+        <v>871.4</v>
       </c>
       <c r="F8">
-        <v>2426.1999999999998</v>
+        <v>2564.5</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -3878,19 +3891,19 @@
         <v>80</v>
       </c>
       <c r="B9">
-        <v>2430.5</v>
+        <v>2512.6</v>
       </c>
       <c r="C9">
-        <v>4241.6000000000004</v>
+        <v>4288.5</v>
       </c>
       <c r="D9">
-        <v>1200.8</v>
+        <v>1233</v>
       </c>
       <c r="E9">
-        <v>946</v>
+        <v>962.6</v>
       </c>
       <c r="F9">
-        <v>2724.4</v>
+        <v>2813.3</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -3898,19 +3911,19 @@
         <v>90</v>
       </c>
       <c r="B10">
-        <v>2803.6</v>
+        <v>2851.7</v>
       </c>
       <c r="C10">
-        <v>4943.1000000000004</v>
+        <v>4900.3999999999996</v>
       </c>
       <c r="D10">
-        <v>1347.1</v>
+        <v>1361.4</v>
       </c>
       <c r="E10">
-        <v>1060.5999999999999</v>
+        <v>1057.8</v>
       </c>
       <c r="F10">
-        <v>3140</v>
+        <v>3113.1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -3918,19 +3931,19 @@
         <v>100</v>
       </c>
       <c r="B11">
-        <v>2934</v>
+        <v>3166.1</v>
       </c>
       <c r="C11">
-        <v>5330.8</v>
+        <v>5476.1</v>
       </c>
       <c r="D11">
-        <v>1431.4</v>
+        <v>1493</v>
       </c>
       <c r="E11">
-        <v>1112.5999999999999</v>
+        <v>1150.7</v>
       </c>
       <c r="F11">
-        <v>3248.6</v>
+        <v>3455</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -4169,19 +4182,19 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <v>169.6</v>
+        <v>208.4</v>
       </c>
       <c r="C2">
-        <v>197.6</v>
+        <v>224.8</v>
       </c>
       <c r="D2">
-        <v>128.80000000000001</v>
+        <v>130.6</v>
       </c>
       <c r="E2">
-        <v>140</v>
+        <v>147.30000000000001</v>
       </c>
       <c r="F2">
-        <v>148.5</v>
+        <v>181.9</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4189,19 +4202,19 @@
         <v>20</v>
       </c>
       <c r="B3">
-        <v>366.4</v>
+        <v>449.3</v>
       </c>
       <c r="C3">
-        <v>478</v>
+        <v>504.1</v>
       </c>
       <c r="D3">
-        <v>186.6</v>
+        <v>200.8</v>
       </c>
       <c r="E3">
-        <v>197.2</v>
+        <v>205.4</v>
       </c>
       <c r="F3">
-        <v>315.8</v>
+        <v>356.3</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -4209,19 +4222,19 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>566.6</v>
+        <v>665</v>
       </c>
       <c r="C4">
-        <v>789.9</v>
+        <v>785.6</v>
       </c>
       <c r="D4">
-        <v>232.6</v>
+        <v>231.4</v>
       </c>
       <c r="E4">
-        <v>247.4</v>
+        <v>250.7</v>
       </c>
       <c r="F4">
-        <v>477.9</v>
+        <v>501</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -4229,19 +4242,19 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>772.4</v>
+        <v>867.4</v>
       </c>
       <c r="C5">
-        <v>1049.9000000000001</v>
+        <v>1074.4000000000001</v>
       </c>
       <c r="D5">
-        <v>268.2</v>
+        <v>273.39999999999998</v>
       </c>
       <c r="E5">
-        <v>292.39999999999998</v>
+        <v>296</v>
       </c>
       <c r="F5">
-        <v>608.6</v>
+        <v>673.4</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -4249,19 +4262,19 @@
         <v>50</v>
       </c>
       <c r="B6">
-        <v>986.2</v>
+        <v>1077.0999999999999</v>
       </c>
       <c r="C6">
-        <v>1330.9</v>
+        <v>1377.6</v>
       </c>
       <c r="D6">
-        <v>299</v>
+        <v>308.60000000000002</v>
       </c>
       <c r="E6">
-        <v>339.2</v>
+        <v>341.6</v>
       </c>
       <c r="F6">
-        <v>743.5</v>
+        <v>815.2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -4269,19 +4282,19 @@
         <v>60</v>
       </c>
       <c r="B7">
-        <v>1172.3</v>
+        <v>1294.7</v>
       </c>
       <c r="C7">
-        <v>1586.2</v>
+        <v>1639.1</v>
       </c>
       <c r="D7">
-        <v>351.4</v>
+        <v>347</v>
       </c>
       <c r="E7">
-        <v>381.4</v>
+        <v>379</v>
       </c>
       <c r="F7">
-        <v>913.2</v>
+        <v>953.8</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -4289,19 +4302,19 @@
         <v>70</v>
       </c>
       <c r="B8">
-        <v>1410.4</v>
+        <v>1592.4</v>
       </c>
       <c r="C8">
-        <v>1859.4</v>
+        <v>1885.2</v>
       </c>
       <c r="D8">
-        <v>385.1</v>
+        <v>375.5</v>
       </c>
       <c r="E8">
-        <v>428.1</v>
+        <v>418.5</v>
       </c>
       <c r="F8">
-        <v>1049.2</v>
+        <v>1101.3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -4309,19 +4322,19 @@
         <v>80</v>
       </c>
       <c r="B9">
-        <v>1581</v>
+        <v>1813</v>
       </c>
       <c r="C9">
-        <v>2139.4</v>
+        <v>2185.9</v>
       </c>
       <c r="D9">
-        <v>421.2</v>
+        <v>423.6</v>
       </c>
       <c r="E9">
-        <v>467.6</v>
+        <v>470.7</v>
       </c>
       <c r="F9">
-        <v>1170.5999999999999</v>
+        <v>1208.8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -4329,19 +4342,19 @@
         <v>90</v>
       </c>
       <c r="B10">
-        <v>1863.4</v>
+        <v>2094.4</v>
       </c>
       <c r="C10">
-        <v>2515.1999999999998</v>
+        <v>2489.9</v>
       </c>
       <c r="D10">
-        <v>468.2</v>
+        <v>459.1</v>
       </c>
       <c r="E10">
-        <v>524</v>
+        <v>517.4</v>
       </c>
       <c r="F10">
-        <v>1346.1</v>
+        <v>1352.2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -4349,19 +4362,19 @@
         <v>100</v>
       </c>
       <c r="B11">
-        <v>1920.4</v>
+        <v>2293.4</v>
       </c>
       <c r="C11">
-        <v>2719.1</v>
+        <v>2803.9</v>
       </c>
       <c r="D11">
-        <v>504.9</v>
+        <v>497.6</v>
       </c>
       <c r="E11">
-        <v>559.20000000000005</v>
+        <v>569</v>
       </c>
       <c r="F11">
-        <v>1394</v>
+        <v>1473.7</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
